--- a/tests/resources/data2.xlsx
+++ b/tests/resources/data2.xlsx
@@ -5,24 +5,25 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="List 1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="OneDiff" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="MoreDiffs" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="DiffsAndRowsNumberDiff" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="RowsNumberDiff" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t xml:space="preserve">Product ID</t>
   </si>
@@ -42,9 +43,6 @@
     <t xml:space="preserve">Wireless Mouse</t>
   </si>
   <si>
-    <t xml:space="preserve">25.50</t>
-  </si>
-  <si>
     <t xml:space="preserve">Warehouse A, Shelf 2</t>
   </si>
   <si>
@@ -54,9 +52,6 @@
     <t xml:space="preserve">Keyboard, Mechanical</t>
   </si>
   <si>
-    <t xml:space="preserve">89.99</t>
-  </si>
-  <si>
     <t xml:space="preserve">Store Front</t>
   </si>
   <si>
@@ -66,9 +61,6 @@
     <t xml:space="preserve">Monitor 24-inch</t>
   </si>
   <si>
-    <t xml:space="preserve">150.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paris, France</t>
   </si>
   <si>
@@ -93,10 +85,28 @@
     <t xml:space="preserve">P-303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99</t>
+    <t xml:space="preserve">Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nowhere</t>
   </si>
   <si>
     <t xml:space="preserve">P-203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOL</t>
   </si>
 </sst>
 </file>
@@ -179,7 +189,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -190,6 +200,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -209,77 +223,87 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="n">
+        <v>89.99</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -299,9 +323,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -315,60 +339,60 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>89.99</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C5" s="1" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -376,8 +400,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -387,77 +411,199 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B3:F7"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>89.99</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>89.99</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="C4" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="C5" s="0" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>6969</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
